--- a/Docmentations/status accounting.xlsx
+++ b/Docmentations/status accounting.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="الورقة1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="page1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -292,9 +292,6 @@
     </xf>
     <xf borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -638,7 +635,9 @@
         <v>1.0</v>
       </c>
       <c r="H4" s="7"/>
-      <c r="I4" s="11"/>
+      <c r="I4" s="8">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
@@ -662,7 +661,7 @@
       <c r="G5" s="9">
         <v>1.0</v>
       </c>
-      <c r="H5" s="12"/>
+      <c r="H5" s="11"/>
       <c r="I5" s="10" t="s">
         <v>24</v>
       </c>
@@ -689,7 +688,7 @@
       <c r="G6" s="7">
         <v>3.0</v>
       </c>
-      <c r="H6" s="13"/>
+      <c r="H6" s="12"/>
       <c r="I6" s="8">
         <v>2.0</v>
       </c>
@@ -716,7 +715,7 @@
       <c r="G7" s="9">
         <v>1.0</v>
       </c>
-      <c r="H7" s="12"/>
+      <c r="H7" s="11"/>
       <c r="I7" s="10">
         <v>1.0</v>
       </c>
@@ -743,7 +742,7 @@
       <c r="G8" s="7">
         <v>2.0</v>
       </c>
-      <c r="H8" s="13"/>
+      <c r="H8" s="12"/>
       <c r="I8" s="8">
         <v>1.0</v>
       </c>
@@ -770,7 +769,7 @@
       <c r="G9" s="9">
         <v>4.0</v>
       </c>
-      <c r="H9" s="12"/>
+      <c r="H9" s="11"/>
       <c r="I9" s="10">
         <v>5.0</v>
       </c>
@@ -797,7 +796,7 @@
       <c r="G10" s="7">
         <v>1.0</v>
       </c>
-      <c r="H10" s="13"/>
+      <c r="H10" s="12"/>
       <c r="I10" s="8">
         <v>1.0</v>
       </c>
@@ -821,11 +820,11 @@
       <c r="F11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="13">
         <v>5.0</v>
       </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="14">
+      <c r="H11" s="14"/>
+      <c r="I11" s="13">
         <v>4.0</v>
       </c>
     </row>
@@ -848,11 +847,11 @@
       <c r="F12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="H12" s="15"/>
-      <c r="I12" s="14" t="s">
+      <c r="G12" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H12" s="14"/>
+      <c r="I12" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -875,11 +874,11 @@
       <c r="F13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="13">
         <v>3.0</v>
       </c>
-      <c r="H13" s="15"/>
-      <c r="I13" s="14">
+      <c r="H13" s="14"/>
+      <c r="I13" s="13">
         <v>2.0</v>
       </c>
     </row>
@@ -902,11 +901,13 @@
       <c r="F14" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G14" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
+      <c r="G14" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="H14" s="14"/>
+      <c r="I14" s="13">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
@@ -927,11 +928,13 @@
       <c r="F15" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="13">
         <v>5.0</v>
       </c>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="13">
+        <v>6.0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
@@ -952,11 +955,13 @@
       <c r="F16" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="13">
         <v>2.0</v>
       </c>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="13">
+        <v>2.0</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations>
